--- a/artfynd/A 22006-2026 artfynd.xlsx
+++ b/artfynd/A 22006-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100917869</v>
+        <v>100917860</v>
       </c>
       <c r="B2" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,16 +709,17 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Käringberget , Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396600.9523541142</v>
+        <v>396601</v>
       </c>
       <c r="R2" t="n">
-        <v>6704554.704377078</v>
+        <v>6704555</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,19 +749,9 @@
           <t>2022-05-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,51 +778,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100917959</v>
+        <v>100917996</v>
       </c>
       <c r="B3" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Käringberget, Vrm</t>
+          <t>Käringberget , Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>396603.8593655561</v>
+        <v>396682</v>
       </c>
       <c r="R3" t="n">
-        <v>6704552.647400723</v>
+        <v>6704630</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,19 +847,9 @@
           <t>2022-05-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,37 +876,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100917942</v>
+        <v>100917869</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -946,14 +912,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Käringberget, Vrm</t>
+          <t>Käringberget , Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>396603.8593655561</v>
+        <v>396601</v>
       </c>
       <c r="R4" t="n">
-        <v>6704552.647400723</v>
+        <v>6704555</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,19 +949,9 @@
           <t>2022-05-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,58 +978,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100917947</v>
+        <v>79051976</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Käringberget, Vrm</t>
+          <t>Buberget/Busjön, Öster om Ljusnan, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>396603.8593655561</v>
+        <v>396605</v>
       </c>
       <c r="R5" t="n">
-        <v>6704552.647400723</v>
+        <v>6704606</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,22 +1043,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,63 +1068,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Holmqvist</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Holmqvist</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100917952</v>
+        <v>100917844</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Käringberget, Vrm</t>
+          <t>Käringberget , Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>396603.8593655561</v>
+        <v>396608</v>
       </c>
       <c r="R6" t="n">
-        <v>6704552.647400723</v>
+        <v>6704620</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,19 +1153,9 @@
           <t>2022-05-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,15 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100917979</v>
+        <v>100917942</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,18 +1210,22 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Käringberget , Vrm</t>
+          <t>Käringberget, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>396654.4884720376</v>
+        <v>396604</v>
       </c>
       <c r="R7" t="n">
-        <v>6704577.356309278</v>
+        <v>6704553</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1326,19 +1255,9 @@
           <t>2022-05-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,51 +1284,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100917962</v>
+        <v>100917979</v>
       </c>
       <c r="B8" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Käringberget, Vrm</t>
+          <t>Käringberget , Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>396603.8593655561</v>
+        <v>396655</v>
       </c>
       <c r="R8" t="n">
-        <v>6704552.647400723</v>
+        <v>6704578</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1439,19 +1353,9 @@
           <t>2022-05-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,56 +1382,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100917860</v>
+        <v>100917952</v>
       </c>
       <c r="B9" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Käringberget , Vrm</t>
+          <t>Käringberget, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>396600.9523541142</v>
+        <v>396604</v>
       </c>
       <c r="R9" t="n">
-        <v>6704554.704377078</v>
+        <v>6704553</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1557,19 +1451,9 @@
           <t>2022-05-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-05-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,6 +1477,406 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100917959</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Käringberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>396604</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6704553</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100917831</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Käringberget , Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>396608</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6704620</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100917947</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Käringberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>396604</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6704553</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100917962</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Käringberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>396604</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6704553</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Stefan Holmqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22006-2026 artfynd.xlsx
+++ b/artfynd/A 22006-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100917860</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100917996</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100917869</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79051976</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100917844</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100917942</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100917979</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100917952</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100917959</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100917831</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100917947</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1877,8 +1937,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100917962</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>